--- a/src/fixtures/sample/gstr2b-2026-01.xlsx
+++ b/src/fixtures/sample/gstr2b-2026-01.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,25 +470,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C6" t="str">
-        <v>S01/2025/031</v>
+        <v>S01/2025/012</v>
       </c>
       <c r="D6" t="str">
-        <v>06/12/2025</v>
+        <v>02/10/2025</v>
       </c>
       <c r="E6">
-        <v>579380</v>
+        <v>575840</v>
       </c>
       <c r="F6">
-        <v>491000</v>
+        <v>488000</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>44190</v>
+        <v>43920</v>
       </c>
       <c r="I6">
-        <v>44190</v>
+        <v>43920</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>2026-02</v>
       </c>
       <c r="L6" t="str">
-        <v>16/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -517,25 +517,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C7" t="str">
-        <v>S01/2026/041</v>
+        <v>S01/2025/031</v>
       </c>
       <c r="D7" t="str">
-        <v>18/01/2026</v>
+        <v>10/12/2025</v>
       </c>
       <c r="E7">
-        <v>566400</v>
+        <v>575840</v>
       </c>
       <c r="F7">
-        <v>480000</v>
+        <v>488000</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>43200</v>
+        <v>43920</v>
       </c>
       <c r="I7">
-        <v>43200</v>
+        <v>43920</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>2026-02</v>
       </c>
       <c r="L7" t="str">
-        <v>15/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -564,25 +564,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C8" t="str">
-        <v>S01/2026/043</v>
+        <v>S01/2025/033</v>
       </c>
       <c r="D8" t="str">
-        <v>12/01/2026</v>
+        <v>17/12/2025</v>
       </c>
       <c r="E8">
-        <v>561680</v>
+        <v>580560</v>
       </c>
       <c r="F8">
-        <v>476000</v>
+        <v>492000</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>42840</v>
+        <v>44280</v>
       </c>
       <c r="I8">
-        <v>42840</v>
+        <v>44280</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>2026-02</v>
       </c>
       <c r="L8" t="str">
-        <v>15/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -614,16 +614,16 @@
         <v>S05/2026/041</v>
       </c>
       <c r="D9" t="str">
-        <v>24/01/2026</v>
+        <v>10/01/2026</v>
       </c>
       <c r="E9">
-        <v>362260</v>
+        <v>356360</v>
       </c>
       <c r="F9">
-        <v>307000</v>
+        <v>302000</v>
       </c>
       <c r="G9">
-        <v>55260</v>
+        <v>54360</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>2026-02</v>
       </c>
       <c r="L9" t="str">
-        <v>09/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -661,16 +661,16 @@
         <v>S05/2026/042</v>
       </c>
       <c r="D10" t="str">
-        <v>02/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="E10">
-        <v>363440</v>
+        <v>351640</v>
       </c>
       <c r="F10">
-        <v>308000</v>
+        <v>298000</v>
       </c>
       <c r="G10">
-        <v>55440</v>
+        <v>53640</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>2026-02</v>
       </c>
       <c r="L10" t="str">
-        <v>16/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
@@ -708,16 +708,16 @@
         <v>S05/2026/043</v>
       </c>
       <c r="D11" t="str">
-        <v>25/01/2026</v>
+        <v>05/01/2026</v>
       </c>
       <c r="E11">
-        <v>365800</v>
+        <v>363440</v>
       </c>
       <c r="F11">
-        <v>310000</v>
+        <v>308000</v>
       </c>
       <c r="G11">
-        <v>55800</v>
+        <v>55440</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>2026-02</v>
       </c>
       <c r="L11" t="str">
-        <v>10/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -755,22 +755,22 @@
         <v>SE 41</v>
       </c>
       <c r="D12" t="str">
-        <v>24/01/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="E12">
-        <v>168740</v>
+        <v>177000</v>
       </c>
       <c r="F12">
-        <v>143000</v>
+        <v>150000</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>12870</v>
+        <v>13500</v>
       </c>
       <c r="I12">
-        <v>12870</v>
+        <v>13500</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>2026-02</v>
       </c>
       <c r="L12" t="str">
-        <v>15/02/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="M12" t="str">
         <v>Yes</v>
@@ -802,22 +802,22 @@
         <v>SE 41</v>
       </c>
       <c r="D13" t="str">
-        <v>08/01/2026</v>
+        <v>05/01/2026</v>
       </c>
       <c r="E13">
-        <v>179360</v>
+        <v>181720</v>
       </c>
       <c r="F13">
-        <v>152000</v>
+        <v>154000</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>13680</v>
+        <v>13860</v>
       </c>
       <c r="I13">
-        <v>13680</v>
+        <v>13860</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2026-02</v>
       </c>
       <c r="L13" t="str">
-        <v>11/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="M13" t="str">
         <v>Yes</v>
@@ -849,22 +849,22 @@
         <v>S07/2026/041</v>
       </c>
       <c r="D14" t="str">
-        <v>23/01/2026</v>
+        <v>03/01/2026</v>
       </c>
       <c r="E14">
-        <v>250160</v>
+        <v>234820</v>
       </c>
       <c r="F14">
-        <v>212000</v>
+        <v>199000</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>19080</v>
+        <v>17910</v>
       </c>
       <c r="I14">
-        <v>19080</v>
+        <v>17910</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>2026-02</v>
       </c>
       <c r="L14" t="str">
-        <v>15/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="M14" t="str">
         <v>Yes</v>
@@ -896,22 +896,22 @@
         <v>S07/2026/042</v>
       </c>
       <c r="D15" t="str">
-        <v>25/01/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="E15">
-        <v>231280</v>
+        <v>237180</v>
       </c>
       <c r="F15">
-        <v>196000</v>
+        <v>201000</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>17640</v>
+        <v>18090</v>
       </c>
       <c r="I15">
-        <v>17640</v>
+        <v>18090</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>2026-02</v>
       </c>
       <c r="L15" t="str">
-        <v>16/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="M15" t="str">
         <v>Yes</v>
@@ -943,16 +943,16 @@
         <v>S08/2026/041</v>
       </c>
       <c r="D16" t="str">
-        <v>02/01/2026</v>
+        <v>19/01/2026</v>
       </c>
       <c r="E16">
-        <v>210040</v>
+        <v>214760</v>
       </c>
       <c r="F16">
-        <v>178000</v>
+        <v>182000</v>
       </c>
       <c r="G16">
-        <v>32040</v>
+        <v>32760</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>2026-02</v>
       </c>
       <c r="L16" t="str">
-        <v>08/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="M16" t="str">
         <v>Yes</v>
@@ -990,16 +990,16 @@
         <v>S08/2026/042</v>
       </c>
       <c r="D17" t="str">
-        <v>22/01/2026</v>
+        <v>10/01/2026</v>
       </c>
       <c r="E17">
-        <v>218300</v>
+        <v>224200</v>
       </c>
       <c r="F17">
-        <v>185000</v>
+        <v>190000</v>
       </c>
       <c r="G17">
-        <v>33300</v>
+        <v>34200</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>2026-02</v>
       </c>
       <c r="L17" t="str">
-        <v>16/02/2026</v>
+        <v>11/02/2026</v>
       </c>
       <c r="M17" t="str">
         <v>Yes</v>
@@ -1037,22 +1037,22 @@
         <v>S09/2026/041</v>
       </c>
       <c r="D18" t="str">
-        <v>02/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="E18">
-        <v>1044300</v>
+        <v>1039580</v>
       </c>
       <c r="F18">
-        <v>885000</v>
+        <v>881000</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>79650</v>
+        <v>79290</v>
       </c>
       <c r="I18">
-        <v>79650</v>
+        <v>79290</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>2026-02</v>
       </c>
       <c r="L18" t="str">
-        <v>16/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="M18" t="str">
         <v>No</v>
@@ -1084,16 +1084,16 @@
         <v>S10/2026/041</v>
       </c>
       <c r="D19" t="str">
-        <v>24/01/2026</v>
+        <v>04/01/2026</v>
       </c>
       <c r="E19">
-        <v>310340</v>
+        <v>304440</v>
       </c>
       <c r="F19">
-        <v>263000</v>
+        <v>258000</v>
       </c>
       <c r="G19">
-        <v>47340</v>
+        <v>46440</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>2026-02</v>
       </c>
       <c r="L19" t="str">
-        <v>15/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="M19" t="str">
         <v>Yes</v>
@@ -1131,16 +1131,16 @@
         <v>S10/2026/042</v>
       </c>
       <c r="D20" t="str">
-        <v>19/01/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="E20">
-        <v>316240</v>
+        <v>315060</v>
       </c>
       <c r="F20">
-        <v>268000</v>
+        <v>267000</v>
       </c>
       <c r="G20">
-        <v>48240</v>
+        <v>48060</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>2026-02</v>
       </c>
       <c r="L20" t="str">
-        <v>14/02/2026</v>
+        <v>15/02/2026</v>
       </c>
       <c r="M20" t="str">
         <v>Yes</v>
@@ -1178,22 +1178,22 @@
         <v>S12/2026/041</v>
       </c>
       <c r="D21" t="str">
-        <v>08/01/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="E21">
-        <v>186440</v>
+        <v>177000</v>
       </c>
       <c r="F21">
-        <v>158000</v>
+        <v>150000</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>14220</v>
+        <v>13500</v>
       </c>
       <c r="I21">
-        <v>14220</v>
+        <v>13500</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>2026-02</v>
       </c>
       <c r="L21" t="str">
-        <v>10/02/2026</v>
+        <v>11/02/2026</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
@@ -1225,22 +1225,22 @@
         <v>S12/2026/042</v>
       </c>
       <c r="D22" t="str">
-        <v>23/01/2026</v>
+        <v>06/01/2026</v>
       </c>
       <c r="E22">
-        <v>184080</v>
+        <v>198240</v>
       </c>
       <c r="F22">
-        <v>156000</v>
+        <v>168000</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>14040</v>
+        <v>15120</v>
       </c>
       <c r="I22">
-        <v>14040</v>
+        <v>15120</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>2026-02</v>
       </c>
       <c r="L22" t="str">
-        <v>12/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="M22" t="str">
         <v>Yes</v>
@@ -1272,22 +1272,22 @@
         <v>S13/2026/041</v>
       </c>
       <c r="D23" t="str">
-        <v>26/01/2026</v>
+        <v>18/01/2026</v>
       </c>
       <c r="E23">
-        <v>88500</v>
+        <v>86140</v>
       </c>
       <c r="F23">
-        <v>75000</v>
+        <v>73000</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>6750</v>
+        <v>6570</v>
       </c>
       <c r="I23">
-        <v>6750</v>
+        <v>6570</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2026-02</v>
       </c>
       <c r="L23" t="str">
-        <v>08/02/2026</v>
+        <v>12/02/2026</v>
       </c>
       <c r="M23" t="str">
         <v>Yes</v>
@@ -1319,16 +1319,16 @@
         <v>S14/2026/041</v>
       </c>
       <c r="D24" t="str">
-        <v>10/01/2026</v>
+        <v>24/01/2026</v>
       </c>
       <c r="E24">
-        <v>153400</v>
+        <v>149860</v>
       </c>
       <c r="F24">
-        <v>130000</v>
+        <v>127000</v>
       </c>
       <c r="G24">
-        <v>23400</v>
+        <v>22860</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>2026-02</v>
       </c>
       <c r="L24" t="str">
-        <v>13/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
@@ -1363,19 +1363,19 @@
         <v>Lakshmi Fasteners</v>
       </c>
       <c r="C25" t="str">
-        <v>S15/2025/031</v>
+        <v>S15/2026/041</v>
       </c>
       <c r="D25" t="str">
-        <v>18/12/2025</v>
+        <v>12/01/2026</v>
       </c>
       <c r="E25">
-        <v>33040</v>
+        <v>50740</v>
       </c>
       <c r="F25">
-        <v>28000</v>
+        <v>43000</v>
       </c>
       <c r="G25">
-        <v>5040</v>
+        <v>7740</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>2026-02</v>
       </c>
       <c r="L25" t="str">
-        <v>11/02/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="M25" t="str">
         <v>Yes</v>
@@ -1410,19 +1410,19 @@
         <v>Lakshmi Fasteners</v>
       </c>
       <c r="C26" t="str">
-        <v>S15/2026/041</v>
+        <v>S15/2026/042</v>
       </c>
       <c r="D26" t="str">
-        <v>16/01/2026</v>
+        <v>25/01/2026</v>
       </c>
       <c r="E26">
-        <v>33040</v>
+        <v>43660</v>
       </c>
       <c r="F26">
-        <v>28000</v>
+        <v>37000</v>
       </c>
       <c r="G26">
-        <v>5040</v>
+        <v>6660</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>2026-02</v>
       </c>
       <c r="L26" t="str">
-        <v>16/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="M26" t="str">
         <v>Yes</v>
@@ -1457,19 +1457,19 @@
         <v>Lakshmi Fasteners</v>
       </c>
       <c r="C27" t="str">
-        <v>S15/2026/042</v>
+        <v>S15/2026/043</v>
       </c>
       <c r="D27" t="str">
-        <v>26/01/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="E27">
-        <v>44840</v>
+        <v>47200</v>
       </c>
       <c r="F27">
-        <v>38000</v>
+        <v>40000</v>
       </c>
       <c r="G27">
-        <v>6840</v>
+        <v>7200</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>2026-02</v>
       </c>
       <c r="L27" t="str">
-        <v>14/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="M27" t="str">
         <v>Yes</v>
@@ -1498,25 +1498,25 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>33AAJFL7745T1ZE</v>
+        <v>29AAECO9912W1Z8</v>
       </c>
       <c r="B28" t="str">
-        <v>Lakshmi Fasteners</v>
+        <v>Orion Software Services</v>
       </c>
       <c r="C28" t="str">
-        <v>S15/2026/043</v>
+        <v>S16/2026/041</v>
       </c>
       <c r="D28" t="str">
-        <v>05/01/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="E28">
-        <v>49560</v>
+        <v>81420</v>
       </c>
       <c r="F28">
-        <v>42000</v>
+        <v>69000</v>
       </c>
       <c r="G28">
-        <v>7560</v>
+        <v>12420</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>2026-02</v>
       </c>
       <c r="L28" t="str">
-        <v>13/02/2026</v>
+        <v>15/02/2026</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
@@ -1551,19 +1551,19 @@
         <v>Orion Software Services</v>
       </c>
       <c r="C29" t="str">
-        <v>S16/2026/041</v>
+        <v>S16/2026/042</v>
       </c>
       <c r="D29" t="str">
-        <v>24/01/2026</v>
+        <v>04/01/2026</v>
       </c>
       <c r="E29">
-        <v>67260</v>
+        <v>76700</v>
       </c>
       <c r="F29">
-        <v>57000</v>
+        <v>65000</v>
       </c>
       <c r="G29">
-        <v>10260</v>
+        <v>11700</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>2026-02</v>
       </c>
       <c r="L29" t="str">
-        <v>11/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="M29" t="str">
         <v>Yes</v>
@@ -1592,25 +1592,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>29AAECO9912W1Z8</v>
+        <v>09AAHFG4423Y1ZH</v>
       </c>
       <c r="B30" t="str">
-        <v>Orion Software Services</v>
+        <v>Ganga Textiles</v>
       </c>
       <c r="C30" t="str">
-        <v>S16/2026/042</v>
+        <v>S17/2026/041</v>
       </c>
       <c r="D30" t="str">
         <v>11/01/2026</v>
       </c>
       <c r="E30">
-        <v>81420</v>
+        <v>59000</v>
       </c>
       <c r="F30">
-        <v>69000</v>
+        <v>50000</v>
       </c>
       <c r="G30">
-        <v>12420</v>
+        <v>9000</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1639,31 +1639,31 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>09AAHFG4423Y1ZH</v>
+        <v>27AAKFP6678U1ZU</v>
       </c>
       <c r="B31" t="str">
-        <v>Ganga Textiles</v>
+        <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C31" t="str">
-        <v>S17/2026/041</v>
+        <v>S18/2026/041</v>
       </c>
       <c r="D31" t="str">
-        <v>22/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="E31">
-        <v>47200</v>
+        <v>160480</v>
       </c>
       <c r="F31">
-        <v>40000</v>
+        <v>136000</v>
       </c>
       <c r="G31">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>12240</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>12240</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1692,25 +1692,25 @@
         <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C32" t="str">
-        <v>S18/2026/041</v>
+        <v>S18/2026/042</v>
       </c>
       <c r="D32" t="str">
-        <v>04/01/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="E32">
-        <v>165200</v>
+        <v>169920</v>
       </c>
       <c r="F32">
-        <v>140000</v>
+        <v>144000</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>12600</v>
+        <v>12960</v>
       </c>
       <c r="I32">
-        <v>12600</v>
+        <v>12960</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1719,7 +1719,7 @@
         <v>2026-02</v>
       </c>
       <c r="L32" t="str">
-        <v>13/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="M32" t="str">
         <v>Yes</v>
@@ -1739,25 +1739,25 @@
         <v>Pinnacle Safety Gear</v>
       </c>
       <c r="C33" t="str">
-        <v>S18/2026/042</v>
+        <v>S18/2026/043</v>
       </c>
       <c r="D33" t="str">
-        <v>15/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="E33">
-        <v>145140</v>
+        <v>171100</v>
       </c>
       <c r="F33">
-        <v>123000</v>
+        <v>145000</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>11070</v>
+        <v>13050</v>
       </c>
       <c r="I33">
-        <v>11070</v>
+        <v>13050</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1780,31 +1780,31 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>27AAKFP6678U1ZU</v>
+        <v>33AABFS2234V1ZT</v>
       </c>
       <c r="B34" t="str">
-        <v>Pinnacle Safety Gear</v>
+        <v>Sundar Printing Works</v>
       </c>
       <c r="C34" t="str">
-        <v>S18/2026/043</v>
+        <v>S19/2026/041</v>
       </c>
       <c r="D34" t="str">
-        <v>20/01/2026</v>
+        <v>04/01/2026</v>
       </c>
       <c r="E34">
-        <v>156940</v>
+        <v>110920</v>
       </c>
       <c r="F34">
-        <v>133000</v>
+        <v>94000</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>16920</v>
       </c>
       <c r="H34">
-        <v>11970</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>11970</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>2026-02</v>
       </c>
       <c r="L34" t="str">
-        <v>09/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="M34" t="str">
         <v>Yes</v>
@@ -1827,31 +1827,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B35" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C35" t="str">
-        <v>S19/2026/041</v>
+        <v>S20/2025/032</v>
       </c>
       <c r="D35" t="str">
-        <v>04/01/2026</v>
+        <v>11/12/2025</v>
       </c>
       <c r="E35">
-        <v>101480</v>
+        <v>140420</v>
       </c>
       <c r="F35">
-        <v>86000</v>
+        <v>119000</v>
       </c>
       <c r="G35">
-        <v>15480</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>10710</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>10710</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>2026-02</v>
       </c>
       <c r="L35" t="str">
-        <v>13/02/2026</v>
+        <v>12/02/2026</v>
       </c>
       <c r="M35" t="str">
         <v>Yes</v>
@@ -1874,31 +1874,31 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B36" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C36" t="str">
-        <v>S19/2026/042</v>
+        <v>S20/2026/041</v>
       </c>
       <c r="D36" t="str">
-        <v>18/01/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="E36">
-        <v>96760</v>
+        <v>151040</v>
       </c>
       <c r="F36">
-        <v>82000</v>
+        <v>128000</v>
       </c>
       <c r="G36">
-        <v>14760</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>11520</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>11520</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>2026-02</v>
       </c>
       <c r="L36" t="str">
-        <v>09/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
@@ -1927,25 +1927,25 @@
         <v>Ashoka Civil Works</v>
       </c>
       <c r="C37" t="str">
-        <v>S20/2026/041</v>
+        <v>S20/2026/042</v>
       </c>
       <c r="D37" t="str">
-        <v>24/01/2026</v>
+        <v>04/01/2026</v>
       </c>
       <c r="E37">
-        <v>147500</v>
+        <v>146320</v>
       </c>
       <c r="F37">
-        <v>125000</v>
+        <v>124000</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>11250</v>
+        <v>11160</v>
       </c>
       <c r="I37">
-        <v>11250</v>
+        <v>11160</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2026-02</v>
       </c>
       <c r="L37" t="str">
-        <v>16/02/2026</v>
+        <v>12/02/2026</v>
       </c>
       <c r="M37" t="str">
         <v>Yes</v>
@@ -1968,31 +1968,31 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B38" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C38" t="str">
-        <v>S20/2026/042</v>
+        <v>S21/2026/041</v>
       </c>
       <c r="D38" t="str">
-        <v>14/01/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="E38">
-        <v>149860</v>
+        <v>192340</v>
       </c>
       <c r="F38">
-        <v>127000</v>
+        <v>163000</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>29340</v>
       </c>
       <c r="H38">
-        <v>11430</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>11430</v>
+        <v>0</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>2026-02</v>
       </c>
       <c r="L38" t="str">
-        <v>15/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
@@ -2021,19 +2021,19 @@
         <v>Nova Instruments</v>
       </c>
       <c r="C39" t="str">
-        <v>S21/2026/041</v>
+        <v>S21/2026/042</v>
       </c>
       <c r="D39" t="str">
-        <v>16/01/2026</v>
+        <v>18/01/2026</v>
       </c>
       <c r="E39">
-        <v>185260</v>
+        <v>184080</v>
       </c>
       <c r="F39">
-        <v>157000</v>
+        <v>156000</v>
       </c>
       <c r="G39">
-        <v>28260</v>
+        <v>28080</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>2026-02</v>
       </c>
       <c r="L39" t="str">
-        <v>12/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2068,19 +2068,19 @@
         <v>Nova Instruments</v>
       </c>
       <c r="C40" t="str">
-        <v>S21/2026/042</v>
+        <v>S21/2026/043</v>
       </c>
       <c r="D40" t="str">
-        <v>08/01/2026</v>
+        <v>20/01/2026</v>
       </c>
       <c r="E40">
-        <v>199420</v>
+        <v>186440</v>
       </c>
       <c r="F40">
-        <v>169000</v>
+        <v>158000</v>
       </c>
       <c r="G40">
-        <v>30420</v>
+        <v>28440</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2109,31 +2109,31 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>29AADCN3345Z1ZD</v>
+        <v>27AAGFM1167A1ZO</v>
       </c>
       <c r="B41" t="str">
-        <v>Nova Instruments</v>
+        <v>Meridian Housekeeping</v>
       </c>
       <c r="C41" t="str">
-        <v>S21/2026/043</v>
+        <v>S22/2026/041</v>
       </c>
       <c r="D41" t="str">
-        <v>02/01/2026</v>
+        <v>03/01/2026</v>
       </c>
       <c r="E41">
-        <v>195880</v>
+        <v>219480</v>
       </c>
       <c r="F41">
-        <v>166000</v>
+        <v>186000</v>
       </c>
       <c r="G41">
-        <v>29880</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>16740</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>16740</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>2026-02</v>
       </c>
       <c r="L41" t="str">
-        <v>13/02/2026</v>
+        <v>15/02/2026</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
@@ -2156,31 +2156,31 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>27AAGFM1167A1ZO</v>
+        <v>24AAECC7789B1ZM</v>
       </c>
       <c r="B42" t="str">
-        <v>Meridian Housekeeping</v>
+        <v>Coral Adhesives</v>
       </c>
       <c r="C42" t="str">
-        <v>S22/2026/041</v>
+        <v>S23/2026/041</v>
       </c>
       <c r="D42" t="str">
-        <v>06/01/2026</v>
+        <v>04/01/2026</v>
       </c>
       <c r="E42">
-        <v>219480</v>
+        <v>180540</v>
       </c>
       <c r="F42">
-        <v>186000</v>
+        <v>153000</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>27540</v>
       </c>
       <c r="H42">
-        <v>16740</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>16740</v>
+        <v>0</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>2026-02</v>
       </c>
       <c r="L42" t="str">
-        <v>14/02/2026</v>
+        <v>11/02/2026</v>
       </c>
       <c r="M42" t="str">
         <v>Yes</v>
@@ -2203,25 +2203,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>24AAECC7789B1ZM</v>
+        <v>09AAJFY5523C1Z3</v>
       </c>
       <c r="B43" t="str">
-        <v>Coral Adhesives</v>
+        <v>Yamuna Agro Products</v>
       </c>
       <c r="C43" t="str">
-        <v>S23/2026/041</v>
+        <v>S24/2026/041</v>
       </c>
       <c r="D43" t="str">
-        <v>09/01/2026</v>
+        <v>22/01/2026</v>
       </c>
       <c r="E43">
-        <v>192340</v>
+        <v>169920</v>
       </c>
       <c r="F43">
-        <v>163000</v>
+        <v>144000</v>
       </c>
       <c r="G43">
-        <v>29340</v>
+        <v>25920</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>2026-02</v>
       </c>
       <c r="L43" t="str">
-        <v>12/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="M43" t="str">
         <v>Yes</v>
@@ -2256,19 +2256,19 @@
         <v>Yamuna Agro Products</v>
       </c>
       <c r="C44" t="str">
-        <v>S24/2026/041</v>
+        <v>S24/2026/042</v>
       </c>
       <c r="D44" t="str">
-        <v>15/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="E44">
-        <v>165200</v>
+        <v>146320</v>
       </c>
       <c r="F44">
-        <v>140000</v>
+        <v>124000</v>
       </c>
       <c r="G44">
-        <v>25200</v>
+        <v>22320</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>2026-02</v>
       </c>
       <c r="L44" t="str">
-        <v>13/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="M44" t="str">
         <v>Yes</v>
@@ -2303,19 +2303,19 @@
         <v>Yamuna Agro Products</v>
       </c>
       <c r="C45" t="str">
-        <v>S24/2026/042</v>
+        <v>S24/2026/043</v>
       </c>
       <c r="D45" t="str">
-        <v>15/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="E45">
-        <v>156940</v>
+        <v>169920</v>
       </c>
       <c r="F45">
-        <v>133000</v>
+        <v>144000</v>
       </c>
       <c r="G45">
-        <v>23940</v>
+        <v>25920</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -2330,7 +2330,7 @@
         <v>2026-02</v>
       </c>
       <c r="L45" t="str">
-        <v>13/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="M45" t="str">
         <v>Yes</v>
@@ -2344,31 +2344,31 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09AAJFY5523C1Z3</v>
+        <v>27AABCZ9934D1Z1</v>
       </c>
       <c r="B46" t="str">
-        <v>Yamuna Agro Products</v>
+        <v>Zenith Tooling</v>
       </c>
       <c r="C46" t="str">
-        <v>S24/2026/043</v>
+        <v>S25/2026/041</v>
       </c>
       <c r="D46" t="str">
-        <v>04/01/2026</v>
+        <v>15/01/2026</v>
       </c>
       <c r="E46">
-        <v>151040</v>
+        <v>56640</v>
       </c>
       <c r="F46">
-        <v>128000</v>
+        <v>48000</v>
       </c>
       <c r="G46">
-        <v>23040</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>4320</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>4320</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2389,56 +2389,9 @@
         <v>N</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>27AABCZ9934D1Z1</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Zenith Tooling</v>
-      </c>
-      <c r="C47" t="str">
-        <v>S25/2026/041</v>
-      </c>
-      <c r="D47" t="str">
-        <v>09/01/2026</v>
-      </c>
-      <c r="E47">
-        <v>50740</v>
-      </c>
-      <c r="F47">
-        <v>43000</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>3870</v>
-      </c>
-      <c r="I47">
-        <v>3870</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="str">
-        <v>2026-02</v>
-      </c>
-      <c r="L47" t="str">
-        <v>13/02/2026</v>
-      </c>
-      <c r="M47" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="N47" t="str">
-        <v/>
-      </c>
-      <c r="O47" t="str">
-        <v>N</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O46"/>
   </ignoredErrors>
 </worksheet>
 </file>
